--- a/artfynd/A 63516-2020 artfynd.xlsx
+++ b/artfynd/A 63516-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63516-2020 artfynd.xlsx
+++ b/artfynd/A 63516-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11030,6 +11030,122 @@
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120438877</v>
+      </c>
+      <c r="B85" t="n">
+        <v>91844</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bankera fuligineoalba</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Oljepottorna, Oljepottorna, Vg</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>449223</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6440085</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Brandstorp</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson, Louise Säf</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
